--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -29879,13 +29879,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O177" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R177" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -30038,10 +30038,10 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O178" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="U178" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>975486</v>
+        <v>975491</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -27480,13 +27480,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>9714</v>
+        <v>9743</v>
       </c>
       <c r="O161" t="n">
-        <v>9714</v>
+        <v>9743</v>
       </c>
       <c r="R161" t="n">
-        <v>35.67769401481524</v>
+        <v>35.78420555758132</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -29695,12 +29695,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -29725,22 +29725,22 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N176" t="n">
-        <v>639</v>
+        <v>5459</v>
       </c>
       <c r="O176" t="n">
-        <v>639</v>
+        <v>5459</v>
       </c>
       <c r="R176" t="n">
-        <v>2.346926752673146</v>
+        <v>4.458957096901518</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -29773,42 +29773,42 @@
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29840,12 +29840,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -29879,95 +29879,81 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>8</v>
+        <v>639</v>
       </c>
       <c r="O177" t="n">
-        <v>8</v>
+        <v>639</v>
       </c>
       <c r="R177" t="n">
-        <v>0.142304733669131</v>
+        <v>2.346926752673146</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ177" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS177" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29980,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -30038,103 +30024,28 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O178" t="n">
-        <v>8</v>
+        <v>13</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0.2312451922123379</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U178" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_2801</t>
         </is>
       </c>
-      <c r="V178" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="W178" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X178" t="inlineStr">
-        <is>
-          <t>Coronavirus SARS-CoV-2</t>
-        </is>
-      </c>
-      <c r="Y178" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z178" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB178" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD178" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE178" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF178" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG178" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH178" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI178" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ178" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK178" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
-        </is>
-      </c>
-      <c r="AM178" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN178" t="b">
-        <v>1</v>
       </c>
       <c r="AO178" t="inlineStr">
         <is>
@@ -30200,6 +30111,240 @@
         </is>
       </c>
       <c r="BC178" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>13</v>
+      </c>
+      <c r="O179" t="n">
+        <v>13</v>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN179" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP179" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AT179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV179" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA179" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB179" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC179" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -30321,7 +30466,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10">
@@ -30331,7 +30476,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -30383,7 +30528,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>975491</v>
+        <v>980984</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -27480,13 +27480,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>9743</v>
+        <v>9744</v>
       </c>
       <c r="O161" t="n">
-        <v>9743</v>
+        <v>9744</v>
       </c>
       <c r="R161" t="n">
-        <v>35.78420555758132</v>
+        <v>35.78787836940084</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -30024,13 +30024,13 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O178" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R178" t="n">
-        <v>0.2312451922123379</v>
+        <v>0.2668213756296206</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -30183,10 +30183,10 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O179" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U179" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>980984</v>
+        <v>980987</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -27480,13 +27480,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>9744</v>
+        <v>9745</v>
       </c>
       <c r="O161" t="n">
-        <v>9744</v>
+        <v>9745</v>
       </c>
       <c r="R161" t="n">
-        <v>35.78787836940084</v>
+        <v>35.79155118122036</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -28722,12 +28722,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -28761,95 +28761,84 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>18</v>
+        <v>770671</v>
       </c>
       <c r="O170" t="n">
-        <v>18</v>
+        <v>770671</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>6</v>
       </c>
       <c r="R170" t="n">
-        <v>0.3201856507555447</v>
+        <v>54.54478841089141</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ170" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -28876,7 +28865,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -28925,98 +28914,23 @@
       <c r="O171" t="n">
         <v>18</v>
       </c>
+      <c r="R171" t="n">
+        <v>0.3201856507555447</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U171" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_2801</t>
         </is>
       </c>
-      <c r="V171" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="W171" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X171" t="inlineStr">
-        <is>
-          <t>Coronavirus SARS-CoV-2</t>
-        </is>
-      </c>
-      <c r="Y171" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD171" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE171" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF171" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG171" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH171" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI171" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
-        </is>
-      </c>
-      <c r="AM171" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN171" t="b">
-        <v>1</v>
       </c>
       <c r="AO171" t="inlineStr">
         <is>
@@ -29110,17 +29024,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -29145,7 +29059,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -29154,81 +29068,170 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>6332</v>
+        <v>18</v>
       </c>
       <c r="O172" t="n">
-        <v>6332</v>
-      </c>
-      <c r="R172" t="n">
-        <v>5.172030836706432</v>
-      </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN172" t="b">
+        <v>1</v>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
       <c r="AT172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -29290,7 +29293,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -29299,13 +29302,13 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>6578</v>
+        <v>6332</v>
       </c>
       <c r="O173" t="n">
-        <v>6578</v>
+        <v>6332</v>
       </c>
       <c r="R173" t="n">
-        <v>5.372965704967611</v>
+        <v>5.172030836706432</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -29435,7 +29438,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -29444,13 +29447,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>3896</v>
+        <v>6578</v>
       </c>
       <c r="O174" t="n">
-        <v>3896</v>
+        <v>6578</v>
       </c>
       <c r="R174" t="n">
-        <v>3.182285555876225</v>
+        <v>5.372965704967611</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -29580,7 +29583,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -29589,13 +29592,13 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>4353</v>
+        <v>3896</v>
       </c>
       <c r="O175" t="n">
-        <v>4353</v>
+        <v>3896</v>
       </c>
       <c r="R175" t="n">
-        <v>3.55556699813378</v>
+        <v>3.182285555876225</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -29725,7 +29728,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -29734,13 +29737,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>5459</v>
+        <v>4353</v>
       </c>
       <c r="O176" t="n">
-        <v>5459</v>
+        <v>4353</v>
       </c>
       <c r="R176" t="n">
-        <v>4.458957096901518</v>
+        <v>3.55556699813378</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -29840,12 +29843,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -29870,22 +29873,22 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N177" t="n">
-        <v>639</v>
+        <v>5459</v>
       </c>
       <c r="O177" t="n">
-        <v>639</v>
+        <v>5459</v>
       </c>
       <c r="R177" t="n">
-        <v>2.346926752673146</v>
+        <v>4.458957096901518</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -29918,42 +29921,42 @@
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29985,12 +29988,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -30024,95 +30027,81 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>15</v>
+        <v>639</v>
       </c>
       <c r="O178" t="n">
-        <v>15</v>
+        <v>639</v>
       </c>
       <c r="R178" t="n">
-        <v>0.2668213756296206</v>
+        <v>2.346926752673146</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AA178" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30139,7 +30128,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -30188,98 +30177,23 @@
       <c r="O179" t="n">
         <v>15</v>
       </c>
+      <c r="R179" t="n">
+        <v>0.2668213756296206</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U179" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_2801</t>
         </is>
       </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="W179" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>Coronavirus SARS-CoV-2</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD179" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE179" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF179" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG179" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI179" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
-        </is>
-      </c>
-      <c r="AM179" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN179" t="b">
-        <v>1</v>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
@@ -30345,6 +30259,240 @@
         </is>
       </c>
       <c r="BC179" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v>15</v>
+      </c>
+      <c r="O180" t="n">
+        <v>15</v>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN180" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP180" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AT180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV180" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA180" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB180" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC180" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -30466,7 +30614,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10">
@@ -30476,7 +30624,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -30528,7 +30676,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>980987</v>
+        <v>1751659</v>
       </c>
     </row>
     <row r="16">
@@ -30538,7 +30686,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -28722,12 +28722,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -28761,16 +28761,13 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>770671</v>
+        <v>113</v>
       </c>
       <c r="O170" t="n">
-        <v>770671</v>
-      </c>
-      <c r="Q170" t="n">
-        <v>6</v>
+        <v>113</v>
       </c>
       <c r="R170" t="n">
-        <v>54.54478841089141</v>
+        <v>1.254468628181937</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -28803,42 +28800,42 @@
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -28870,12 +28867,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -28909,95 +28906,84 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>18</v>
+        <v>770671</v>
       </c>
       <c r="O171" t="n">
-        <v>18</v>
+        <v>770671</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>6</v>
       </c>
       <c r="R171" t="n">
-        <v>0.3201856507555447</v>
+        <v>54.54478841089141</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AA171" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ171" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -29024,7 +29010,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -29073,98 +29059,23 @@
       <c r="O172" t="n">
         <v>18</v>
       </c>
+      <c r="R172" t="n">
+        <v>0.3201856507555447</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U172" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_2801</t>
         </is>
       </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>Coronavirus SARS-CoV-2</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD172" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE172" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF172" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG172" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN172" t="b">
-        <v>1</v>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
@@ -29258,17 +29169,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -29293,7 +29204,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -29302,81 +29213,170 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>6332</v>
+        <v>18</v>
       </c>
       <c r="O173" t="n">
-        <v>6332</v>
-      </c>
-      <c r="R173" t="n">
-        <v>5.172030836706432</v>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN173" t="b">
+        <v>1</v>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
       <c r="AT173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -29438,7 +29438,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -29447,13 +29447,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>6578</v>
+        <v>6332</v>
       </c>
       <c r="O174" t="n">
-        <v>6578</v>
+        <v>6332</v>
       </c>
       <c r="R174" t="n">
-        <v>5.372965704967611</v>
+        <v>5.172030836706432</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -29592,13 +29592,13 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>3896</v>
+        <v>6578</v>
       </c>
       <c r="O175" t="n">
-        <v>3896</v>
+        <v>6578</v>
       </c>
       <c r="R175" t="n">
-        <v>3.182285555876225</v>
+        <v>5.372965704967611</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -29737,13 +29737,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>4353</v>
+        <v>3896</v>
       </c>
       <c r="O176" t="n">
-        <v>4353</v>
+        <v>3896</v>
       </c>
       <c r="R176" t="n">
-        <v>3.55556699813378</v>
+        <v>3.182285555876225</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -29882,13 +29882,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>5459</v>
+        <v>4353</v>
       </c>
       <c r="O177" t="n">
-        <v>5459</v>
+        <v>4353</v>
       </c>
       <c r="R177" t="n">
-        <v>4.458957096901518</v>
+        <v>3.55556699813378</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -29988,12 +29988,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -30018,22 +30018,22 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N178" t="n">
-        <v>639</v>
+        <v>5459</v>
       </c>
       <c r="O178" t="n">
-        <v>639</v>
+        <v>5459</v>
       </c>
       <c r="R178" t="n">
-        <v>2.346926752673146</v>
+        <v>4.458957096901518</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -30066,42 +30066,42 @@
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30133,12 +30133,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -30172,95 +30172,81 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>15</v>
+        <v>639</v>
       </c>
       <c r="O179" t="n">
-        <v>15</v>
+        <v>639</v>
       </c>
       <c r="R179" t="n">
-        <v>0.2668213756296206</v>
+        <v>2.346926752673146</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AA179" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ179" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30287,7 +30273,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -30336,98 +30322,23 @@
       <c r="O180" t="n">
         <v>15</v>
       </c>
+      <c r="R180" t="n">
+        <v>0.2668213756296206</v>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U180" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_2801</t>
         </is>
       </c>
-      <c r="V180" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="W180" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X180" t="inlineStr">
-        <is>
-          <t>Coronavirus SARS-CoV-2</t>
-        </is>
-      </c>
-      <c r="Y180" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD180" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE180" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF180" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG180" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH180" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI180" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
-        </is>
-      </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN180" t="b">
-        <v>1</v>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
@@ -30493,6 +30404,240 @@
         </is>
       </c>
       <c r="BC180" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>15</v>
+      </c>
+      <c r="O181" t="n">
+        <v>15</v>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD181" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE181" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF181" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG181" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI181" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM181" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN181" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP181" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ181" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AT181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU181" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV181" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW181" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX181" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA181" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB181" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC181" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -30614,7 +30759,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10">
@@ -30624,7 +30769,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -30676,7 +30821,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1751659</v>
+        <v>1751772</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -30317,13 +30317,13 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O180" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="R180" t="n">
-        <v>0.2668213756296206</v>
+        <v>0.3201856507555447</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -30476,10 +30476,10 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O181" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U181" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1751772</v>
+        <v>1751775</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -27480,13 +27480,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>9745</v>
+        <v>9749</v>
       </c>
       <c r="O161" t="n">
-        <v>9745</v>
+        <v>9749</v>
       </c>
       <c r="R161" t="n">
-        <v>35.79155118122036</v>
+        <v>35.80624242849844</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1751775</v>
+        <v>1751779</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -30317,13 +30317,13 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O180" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="R180" t="n">
-        <v>0.3201856507555447</v>
+        <v>0.4447022927160344</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -30476,10 +30476,10 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O181" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="U181" t="inlineStr">
         <is>
@@ -30640,6 +30640,151 @@
       <c r="BC181" t="inlineStr">
         <is>
           <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>7777</v>
+      </c>
+      <c r="O182" t="n">
+        <v>7777</v>
+      </c>
+      <c r="R182" t="n">
+        <v>6.352318985638964</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr"/>
+      <c r="AT182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV182" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA182" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB182" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC182" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30676,7 +30821,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -30759,7 +30904,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
@@ -30769,7 +30914,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -30821,7 +30966,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1751779</v>
+        <v>1759563</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -26362,13 +26362,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O154" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="R154" t="n">
-        <v>8.870011587752877</v>
+        <v>8.888924192417596</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26521,10 +26521,10 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O155" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
@@ -29408,12 +29408,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -29438,7 +29438,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -29447,56 +29447,70 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>6332</v>
+        <v>441</v>
       </c>
       <c r="O174" t="n">
-        <v>6332</v>
+        <v>441</v>
       </c>
       <c r="R174" t="n">
-        <v>5.172030836706432</v>
+        <v>8.340458657140767</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
@@ -29506,17 +29520,17 @@
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
@@ -29548,17 +29562,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -29583,7 +29597,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -29592,56 +29606,145 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>6578</v>
+        <v>441</v>
       </c>
       <c r="O175" t="n">
-        <v>6578</v>
-      </c>
-      <c r="R175" t="n">
-        <v>5.372965704967611</v>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>441</v>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly COVID-19 notifications under the source reporting definition.</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN175" t="b">
+        <v>1</v>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS175" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -29651,17 +29754,17 @@
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
@@ -29728,7 +29831,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -29737,13 +29840,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>3896</v>
+        <v>6332</v>
       </c>
       <c r="O176" t="n">
-        <v>3896</v>
+        <v>6332</v>
       </c>
       <c r="R176" t="n">
-        <v>3.182285555876225</v>
+        <v>5.172030836706432</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -29873,7 +29976,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -29882,13 +29985,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>4353</v>
+        <v>6578</v>
       </c>
       <c r="O177" t="n">
-        <v>4353</v>
+        <v>6578</v>
       </c>
       <c r="R177" t="n">
-        <v>3.55556699813378</v>
+        <v>5.372965704967611</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -30018,7 +30121,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -30027,13 +30130,13 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>5459</v>
+        <v>3896</v>
       </c>
       <c r="O178" t="n">
-        <v>5459</v>
+        <v>3896</v>
       </c>
       <c r="R178" t="n">
-        <v>4.458957096901518</v>
+        <v>3.182285555876225</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -30133,12 +30236,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -30163,22 +30266,22 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N179" t="n">
-        <v>639</v>
+        <v>4353</v>
       </c>
       <c r="O179" t="n">
-        <v>639</v>
+        <v>4353</v>
       </c>
       <c r="R179" t="n">
-        <v>2.346926752673146</v>
+        <v>3.55556699813378</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
@@ -30211,42 +30314,42 @@
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30278,12 +30381,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -30308,104 +30411,90 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N180" t="n">
-        <v>25</v>
+        <v>5459</v>
       </c>
       <c r="O180" t="n">
-        <v>25</v>
+        <v>5459</v>
       </c>
       <c r="R180" t="n">
-        <v>0.4447022927160344</v>
+        <v>4.458957096901518</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30432,17 +30521,17 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -30476,170 +30565,81 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>25</v>
+        <v>639</v>
       </c>
       <c r="O181" t="n">
-        <v>25</v>
-      </c>
-      <c r="U181" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="V181" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>Coronavirus SARS-CoV-2</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA181" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD181" t="inlineStr">
+        <v>639</v>
+      </c>
+      <c r="R181" t="n">
+        <v>2.346926752673146</v>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO181" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP181" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS181" t="inlineStr"/>
+      <c r="AT181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU181" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV181" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE181" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF181" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG181" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ181" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
-        </is>
-      </c>
-      <c r="AM181" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN181" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO181" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP181" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ181" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS181" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AT181" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU181" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV181" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30671,118 +30671,511 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>25</v>
+      </c>
+      <c r="O182" t="n">
+        <v>25</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0.4447022927160344</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AT182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV182" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA182" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB182" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC182" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
+        <v>25</v>
+      </c>
+      <c r="O183" t="n">
+        <v>25</v>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN183" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP183" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ183" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AT183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU183" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV183" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA183" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB183" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC183" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
+      <c r="G184" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>D004</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>COVID-19</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
         <is>
           <t>新型冠状病毒感染</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
+      <c r="K184" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
+      <c r="L184" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr">
+      <c r="M184" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N182" t="n">
+      <c r="N184" t="n">
         <v>7777</v>
       </c>
-      <c r="O182" t="n">
+      <c r="O184" t="n">
         <v>7777</v>
       </c>
-      <c r="R182" t="n">
+      <c r="R184" t="n">
         <v>6.352318985638964</v>
       </c>
-      <c r="S182" t="inlineStr">
+      <c r="S184" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO182" t="inlineStr">
+      <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP182" t="inlineStr">
+      <c r="AP184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR182" t="inlineStr">
+      <c r="AR184" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS182" t="inlineStr"/>
-      <c r="AT182" t="n">
+      <c r="AS184" t="inlineStr"/>
+      <c r="AT184" t="n">
         <v>0</v>
       </c>
-      <c r="AU182" t="inlineStr">
+      <c r="AU184" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV182" t="inlineStr">
+      <c r="AV184" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW182" t="inlineStr">
+      <c r="AW184" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX182" t="inlineStr">
+      <c r="AX184" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY182" t="inlineStr">
+      <c r="AY184" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ182" t="inlineStr">
+      <c r="AZ184" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA182" t="inlineStr">
+      <c r="BA184" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB182" t="inlineStr">
+      <c r="BB184" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC182" t="inlineStr">
+      <c r="BC184" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -30904,7 +31297,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10">
@@ -30914,7 +31307,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -30934,7 +31327,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -30966,7 +31359,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1759563</v>
+        <v>1760005</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -30710,13 +30710,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O182" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R182" t="n">
-        <v>0.4447022927160344</v>
+        <v>0.4980665678419585</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -30869,10 +30869,10 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O183" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="U183" t="inlineStr">
         <is>
@@ -31359,7 +31359,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1760005</v>
+        <v>1760008</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -27480,13 +27480,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>9749</v>
+        <v>9748</v>
       </c>
       <c r="O161" t="n">
-        <v>9749</v>
+        <v>9748</v>
       </c>
       <c r="R161" t="n">
-        <v>35.80624242849844</v>
+        <v>35.80256961667892</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -31359,7 +31359,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1760008</v>
+        <v>1760007</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -27480,13 +27480,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>9748</v>
+        <v>9771</v>
       </c>
       <c r="O161" t="n">
-        <v>9748</v>
+        <v>9771</v>
       </c>
       <c r="R161" t="n">
-        <v>35.80256961667892</v>
+        <v>35.88704428852787</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -29408,12 +29408,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -29447,95 +29447,81 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>441</v>
+        <v>199</v>
       </c>
       <c r="O174" t="n">
-        <v>441</v>
+        <v>199</v>
       </c>
       <c r="R174" t="n">
-        <v>8.340458657140767</v>
+        <v>2.696987857591452</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
-        <is>
-          <t>SER_NZ_COVID19_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA174" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ174" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS174" t="inlineStr">
-        <is>
-          <t>SER_NZ_COVID19_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -29562,7 +29548,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -29611,98 +29597,23 @@
       <c r="O175" t="n">
         <v>441</v>
       </c>
+      <c r="R175" t="n">
+        <v>8.340458657140767</v>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U175" t="inlineStr">
         <is>
           <t>SER_NZ_COVID19_MONTHLY</t>
         </is>
       </c>
-      <c r="V175" t="inlineStr">
-        <is>
-          <t>SER_NZ_COVID19_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W175" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>COVID-19</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD175" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE175" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF175" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG175" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly COVID-19 notifications under the source reporting definition.</t>
-        </is>
-      </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN175" t="b">
-        <v>1</v>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
@@ -29796,17 +29707,17 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -29831,7 +29742,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -29840,56 +29751,145 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>6332</v>
+        <v>441</v>
       </c>
       <c r="O176" t="n">
-        <v>6332</v>
-      </c>
-      <c r="R176" t="n">
-        <v>5.172030836706432</v>
-      </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>441</v>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD176" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE176" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF176" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG176" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly COVID-19 notifications under the source reporting definition.</t>
+        </is>
+      </c>
+      <c r="AM176" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN176" t="b">
+        <v>1</v>
       </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS176" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ176" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr">
+        <is>
+          <t>SER_NZ_COVID19_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -29899,17 +29899,17 @@
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
@@ -29976,7 +29976,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -29985,13 +29985,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>6578</v>
+        <v>6332</v>
       </c>
       <c r="O177" t="n">
-        <v>6578</v>
+        <v>6332</v>
       </c>
       <c r="R177" t="n">
-        <v>5.372965704967611</v>
+        <v>5.172030836706432</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -30130,13 +30130,13 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>3896</v>
+        <v>6578</v>
       </c>
       <c r="O178" t="n">
-        <v>3896</v>
+        <v>6578</v>
       </c>
       <c r="R178" t="n">
-        <v>3.182285555876225</v>
+        <v>5.372965704967611</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -30275,13 +30275,13 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>4353</v>
+        <v>3896</v>
       </c>
       <c r="O179" t="n">
-        <v>4353</v>
+        <v>3896</v>
       </c>
       <c r="R179" t="n">
-        <v>3.55556699813378</v>
+        <v>3.182285555876225</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -30420,13 +30420,13 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>5459</v>
+        <v>4353</v>
       </c>
       <c r="O180" t="n">
-        <v>5459</v>
+        <v>4353</v>
       </c>
       <c r="R180" t="n">
-        <v>4.458957096901518</v>
+        <v>3.55556699813378</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -30526,12 +30526,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -30556,22 +30556,22 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N181" t="n">
-        <v>639</v>
+        <v>5459</v>
       </c>
       <c r="O181" t="n">
-        <v>639</v>
+        <v>5459</v>
       </c>
       <c r="R181" t="n">
-        <v>2.346926752673146</v>
+        <v>4.458957096901518</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
@@ -30604,42 +30604,42 @@
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30671,12 +30671,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -30710,95 +30710,81 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>28</v>
+        <v>639</v>
       </c>
       <c r="O182" t="n">
-        <v>28</v>
+        <v>639</v>
       </c>
       <c r="R182" t="n">
-        <v>0.4980665678419585</v>
+        <v>2.346926752673146</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="AA182" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ182" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr"/>
       <c r="AT182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30825,7 +30811,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -30869,103 +30855,28 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="O183" t="n">
-        <v>28</v>
+        <v>50</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0.8894045854320688</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U183" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_2801</t>
         </is>
       </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_2801</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>Coronavirus SARS-CoV-2</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD183" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE183" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF183" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG183" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN183" t="b">
-        <v>1</v>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
@@ -31059,123 +30970,502 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>50</v>
+      </c>
+      <c r="O184" t="n">
+        <v>50</v>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD184" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE184" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF184" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG184" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM184" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN184" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP184" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AT184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU184" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV184" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA184" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB184" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC184" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
+      <c r="G185" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>D004</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>COVID-19</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
         <is>
           <t>新型冠状病毒感染</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
+      <c r="K185" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
+      <c r="L185" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr">
+      <c r="M185" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N184" t="n">
+      <c r="N185" t="n">
         <v>7777</v>
       </c>
-      <c r="O184" t="n">
+      <c r="O185" t="n">
         <v>7777</v>
       </c>
-      <c r="R184" t="n">
+      <c r="R185" t="n">
         <v>6.352318985638964</v>
       </c>
-      <c r="S184" t="inlineStr">
+      <c r="S185" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO184" t="inlineStr">
+      <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP184" t="inlineStr">
+      <c r="AP185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR184" t="inlineStr">
+      <c r="AR185" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS184" t="inlineStr"/>
-      <c r="AT184" t="n">
+      <c r="AS185" t="inlineStr"/>
+      <c r="AT185" t="n">
         <v>0</v>
       </c>
-      <c r="AU184" t="inlineStr">
+      <c r="AU185" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV184" t="inlineStr">
+      <c r="AV185" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW184" t="inlineStr">
+      <c r="AW185" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX184" t="inlineStr">
+      <c r="AX185" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY184" t="inlineStr">
+      <c r="AY185" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ184" t="inlineStr">
+      <c r="AZ185" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA184" t="inlineStr">
+      <c r="BA185" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB184" t="inlineStr">
+      <c r="BB185" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC184" t="inlineStr">
+      <c r="BC185" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>9122</v>
+      </c>
+      <c r="O186" t="n">
+        <v>9122</v>
+      </c>
+      <c r="R186" t="n">
+        <v>7.45092629381492</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP186" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr"/>
+      <c r="AT186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV186" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA186" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB186" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC186" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -31214,7 +31504,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -31297,7 +31587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -31307,7 +31597,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -31359,7 +31649,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1760007</v>
+        <v>1769373</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -36951,13 +36951,13 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O212" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R212" t="n">
-        <v>1.254468628181937</v>
+        <v>1.265570120466733</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
@@ -41630,13 +41630,13 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>639</v>
+        <v>7354</v>
       </c>
       <c r="O238" t="n">
-        <v>639</v>
+        <v>7354</v>
       </c>
       <c r="R238" t="n">
-        <v>2.346926752673146</v>
+        <v>27.00985812074854</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -41775,13 +41775,13 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="O239" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="R239" t="n">
-        <v>0.8894045854320688</v>
+        <v>1.351894969856744</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -41934,10 +41934,10 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="O240" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="U240" t="inlineStr">
         <is>
@@ -42388,6 +42388,544 @@
       <c r="BC242" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N243" t="n">
+        <v>9826</v>
+      </c>
+      <c r="O243" t="n">
+        <v>9826</v>
+      </c>
+      <c r="R243" t="n">
+        <v>8.025959412741219</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO243" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP243" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr"/>
+      <c r="AT243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU243" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV243" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA243" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB243" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC243" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N244" t="n">
+        <v>0</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AT244" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU244" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV244" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA244" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB244" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC244" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N245" t="n">
+        <v>0</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>Coronavirus SARS-CoV-2</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 2801.</t>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN245" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO245" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP245" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ245" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_2801</t>
+        </is>
+      </c>
+      <c r="AT245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU245" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV245" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA245" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB245" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC245" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -42424,7 +42962,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -42507,7 +43045,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -42517,7 +43055,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -42537,7 +43075,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -42569,7 +43107,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2287909</v>
+        <v>2304477</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -41630,13 +41630,13 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>7354</v>
+        <v>7379</v>
       </c>
       <c r="O238" t="n">
-        <v>7354</v>
+        <v>7379</v>
       </c>
       <c r="R238" t="n">
-        <v>27.00985812074854</v>
+        <v>27.10167841623653</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -43107,7 +43107,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2304477</v>
+        <v>2304502</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -42603,13 +42603,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O244" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R244" t="n">
-        <v>0</v>
+        <v>0.1067285502518482</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -42762,10 +42762,10 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O245" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
@@ -43107,7 +43107,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2304502</v>
+        <v>2304508</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -46811,13 +46811,13 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>9786</v>
+        <v>9785</v>
       </c>
       <c r="O267" t="n">
-        <v>9786</v>
+        <v>9785</v>
       </c>
       <c r="R267" t="n">
-        <v>35.94213646582067</v>
+        <v>35.93846365400115</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -58854,13 +58854,13 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="O335" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="R335" t="n">
-        <v>0.4980665678419585</v>
+        <v>0.6225832098024481</v>
       </c>
       <c r="S335" t="inlineStr">
         <is>
@@ -59013,10 +59013,10 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="O336" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="U336" t="inlineStr">
         <is>
@@ -59358,7 +59358,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2356538</v>
+        <v>2356544</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d004/2026-2029.xlsx
+++ b/diseases/d004/2026-2029.xlsx
@@ -46811,13 +46811,13 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>9785</v>
+        <v>9787</v>
       </c>
       <c r="O267" t="n">
-        <v>9785</v>
+        <v>9787</v>
       </c>
       <c r="R267" t="n">
-        <v>35.93846365400115</v>
+        <v>35.94580927764019</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -54895,13 +54895,13 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>7384</v>
+        <v>7386</v>
       </c>
       <c r="O312" t="n">
-        <v>7384</v>
+        <v>7386</v>
       </c>
       <c r="R312" t="n">
-        <v>27.12004247533413</v>
+        <v>27.12738809897317</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
@@ -58854,13 +58854,13 @@
         </is>
       </c>
       <c r="N335" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="O335" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="R335" t="n">
-        <v>0.6225832098024481</v>
+        <v>0.7115236683456551</v>
       </c>
       <c r="S335" t="inlineStr">
         <is>
@@ -59013,10 +59013,10 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="O336" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="U336" t="inlineStr">
         <is>
@@ -59177,6 +59177,151 @@
       <c r="BC336" t="inlineStr">
         <is>
           <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>covid-19</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N337" t="n">
+        <v>5635</v>
+      </c>
+      <c r="O337" t="n">
+        <v>5635</v>
+      </c>
+      <c r="R337" t="n">
+        <v>4.602715376633093</v>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO337" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP337" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR337" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS337" t="inlineStr"/>
+      <c r="AT337" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU337" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV337" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW337" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX337" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY337" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA337" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB337" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC337" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -59213,7 +59358,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -59296,7 +59441,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
@@ -59306,7 +59451,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11">
@@ -59358,7 +59503,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2356544</v>
+        <v>2362188</v>
       </c>
     </row>
     <row r="16">
